--- a/data/themes/operas/operas.xlsx
+++ b/data/themes/operas/operas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="operas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="operas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>title</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>only_list</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +452,9 @@
           <t>Свадьба Фигаро</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +485,9 @@
           <t>Так поступают все</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -507,6 +518,9 @@
           <t>Похищение из сераля</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -522,6 +536,9 @@
           <t>Фиделио</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -552,6 +569,9 @@
           <t>Волшебный стрелок</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -597,6 +617,9 @@
           <t>Итальянка в Алжире</t>
         </is>
       </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -627,6 +650,9 @@
           <t>Любовный напиток</t>
         </is>
       </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -642,6 +668,9 @@
           <t>Лючия ди Ламмермур</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -657,6 +686,9 @@
           <t>Дон Паскуале</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -672,6 +704,9 @@
           <t>Дочь полка</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -702,6 +737,9 @@
           <t>Сомнамбула</t>
         </is>
       </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -717,6 +755,9 @@
           <t>Пуритане</t>
         </is>
       </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -732,6 +773,9 @@
           <t>Набукко</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -792,6 +836,9 @@
           <t>Травиата</t>
         </is>
       </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -807,6 +854,9 @@
           <t>Сицилийская вечерня</t>
         </is>
       </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -822,6 +872,9 @@
           <t>Симон Бокканегра</t>
         </is>
       </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -852,6 +905,9 @@
           <t>Сила судьбы</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -867,6 +923,9 @@
           <t>Дон Карлос</t>
         </is>
       </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -927,6 +986,9 @@
           <t>Манон Леско</t>
         </is>
       </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -987,6 +1049,9 @@
           <t>Девушка с Запада</t>
         </is>
       </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1032,6 +1097,9 @@
           <t>Сельская честь</t>
         </is>
       </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1062,6 +1130,9 @@
           <t>Андре Шенье</t>
         </is>
       </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1257,6 +1328,9 @@
           <t>Кавалер розы</t>
         </is>
       </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1317,6 +1391,9 @@
           <t>Искатели жемчуга</t>
         </is>
       </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1362,6 +1439,9 @@
           <t>Манон</t>
         </is>
       </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1377,6 +1457,9 @@
           <t>Вертер</t>
         </is>
       </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1392,6 +1475,9 @@
           <t>Тайс</t>
         </is>
       </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1407,6 +1493,9 @@
           <t>Самсон и Далила</t>
         </is>
       </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1422,6 +1511,9 @@
           <t>Лакме</t>
         </is>
       </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1437,6 +1529,9 @@
           <t>Сказки Гофмана</t>
         </is>
       </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1452,6 +1547,9 @@
           <t>Орфей в аду</t>
         </is>
       </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1467,6 +1565,9 @@
           <t>Пеллеас и Мелизанда</t>
         </is>
       </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1482,6 +1583,9 @@
           <t>Проданная невеста</t>
         </is>
       </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1497,6 +1601,9 @@
           <t>Енуфа</t>
         </is>
       </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1512,6 +1619,9 @@
           <t>Замок герцога Синяя Борода</t>
         </is>
       </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1527,6 +1637,9 @@
           <t>Воццек</t>
         </is>
       </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1542,6 +1655,9 @@
           <t>Питер Граймс</t>
         </is>
       </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1557,6 +1673,9 @@
           <t>Порги и Бесс</t>
         </is>
       </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1587,6 +1706,9 @@
           <t>Дидона и Эней</t>
         </is>
       </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1602,6 +1724,9 @@
           <t>Похождения повесы</t>
         </is>
       </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1677,6 +1802,9 @@
           <t>Хованщина</t>
         </is>
       </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1692,6 +1820,9 @@
           <t>Князь Игорь</t>
         </is>
       </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1707,6 +1838,9 @@
           <t>Демон</t>
         </is>
       </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1737,6 +1871,9 @@
           <t>Орлеанская дева</t>
         </is>
       </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1782,6 +1919,9 @@
           <t>Иоланта</t>
         </is>
       </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1827,6 +1967,9 @@
           <t>Царская невеста</t>
         </is>
       </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1857,6 +2000,9 @@
           <t>Сказание о невидимом граде Китеже и деве Февронии</t>
         </is>
       </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1887,6 +2033,9 @@
           <t>Алеко</t>
         </is>
       </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1916,6 +2065,9 @@
         <is>
           <t>Нос</t>
         </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
